--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15228.4</v>
+        <v>14984.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>9.92</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5597014925373134</v>
+        <v>0.5149253731343284</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1535.120967741935</v>
+        <v>1535.266393442623</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07464732978344291</v>
+        <v>0.07484214220284491</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1008064516129032</v>
+        <v>0.1024590163934426</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>44.02985074626866</v>
+        <v>48.50746268656716</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>49.85893191337716</v>
+        <v>49.93685688113796</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>45.77857509640121</v>
+        <v>48.9362809449384</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.2730886508078</v>
+        <v>7.273749899819942</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11165.07088810096</v>
+        <v>11167.1437755002</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2668257408459879</v>
+        <v>-0.2547387397725469</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.11388669312641</v>
+        <v>10.11410710946379</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15526.03952798449</v>
+        <v>15527.84874483886</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.01954502954903314</v>
+        <v>0.03628146613358485</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3824,6 +3824,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B3" s="24" t="n">
+        <v>14984.2</v>
+      </c>
+      <c r="C3" s="25" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="D3" s="26" t="n">
+        <v>0.514925373134</v>
+      </c>
+      <c r="E3" s="26" t="n">
+        <v>0.0748421422028</v>
+      </c>
+      <c r="F3" s="34">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="34">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="34">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -3864,7 +3897,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-30</t>
+          <t>Retrieved 2026-10-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14984.2</v>
+        <v>15094.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>9.76</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5149253731343284</v>
+        <v>0.5373134328358209</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1535.266393442623</v>
+        <v>1535.518819938962</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07484214220284491</v>
+        <v>0.07457826380236887</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1024590163934426</v>
+        <v>0.1017293997965412</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>48.50746268656716</v>
+        <v>46.26865671641791</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>49.93685688113796</v>
+        <v>49.83130552094755</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>48.9362809449384</v>
+        <v>47.3374513577768</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.273749899819942</v>
+        <v>7.272854221134897</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11167.1437755002</v>
+        <v>11167.60453122516</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2547387397725469</v>
+        <v>-0.2601369052762058</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.11410710946379</v>
+        <v>10.11380854990211</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15527.84874483886</v>
+        <v>15529.94336963427</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.03628146613358485</v>
+        <v>0.02887167343866825</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3857,6 +3857,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B4" s="24" t="n">
+        <v>15094.15</v>
+      </c>
+      <c r="C4" s="25" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="D4" s="26" t="n">
+        <v>0.537313432836</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>0.0745782638024</v>
+      </c>
+      <c r="F4" s="34">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="34">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="34">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -3897,7 +3930,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-01</t>
+          <t>Retrieved 2026-10-05</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15094.15</v>
+        <v>15131.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5373134328358209</v>
+        <v>0.5447761194029851</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1535.518819938962</v>
+        <v>1536.223350253807</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07457826380236887</v>
+        <v>0.07544246459377502</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1017293997965412</v>
+        <v>0.1015228426395939</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>46.26865671641791</v>
+        <v>45.52238805970149</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>49.83130552094755</v>
+        <v>50.17698583751</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>47.3374513577768</v>
+        <v>46.91876739304404</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.272854221134897</v>
+        <v>7.275787565535442</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11167.60453122516</v>
+        <v>11177.23474966185</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2601369052762058</v>
+        <v>-0.2613413639050314</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.11380854990211</v>
+        <v>10.11478633136896</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15529.94336963427</v>
+        <v>15538.57094507703</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.02887167343866825</v>
+        <v>0.02688186105268575</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3890,6 +3890,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>15131.8</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.544776119403</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.0754424645938</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -3930,7 +3963,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-05</t>
+          <t>Retrieved 2026-10-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15131.8</v>
+        <v>15004.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>9.85</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5447761194029851</v>
+        <v>0.5149253731343284</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1536.223350253807</v>
+        <v>1535.767656090072</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07544246459377502</v>
+        <v>0.07546681008604161</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1015228426395939</v>
+        <v>0.1023541453428864</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>45.52238805970149</v>
+        <v>48.50746268656716</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>50.17698583751</v>
+        <v>50.18672403441664</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>46.91876739304404</v>
+        <v>49.011241090922</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.275787565535442</v>
+        <v>7.275870201092049</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11177.23474966185</v>
+        <v>11174.04612474674</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2613413639050314</v>
+        <v>-0.2552845239414484</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.11478633136896</v>
+        <v>10.11481387655449</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15538.57094507703</v>
+        <v>15534.00399898343</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.02688186105268575</v>
+        <v>0.03529312963710263</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3923,6 +3923,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>15004.45</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.514925373134</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.07546681008599999</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -3963,7 +3996,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-06</t>
+          <t>Retrieved 2026-10-07</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15004.45</v>
+        <v>14673.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>9.77</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5149253731343284</v>
+        <v>0.5074626865671642</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1535.767656090072</v>
+        <v>1534.932008368201</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07546681008604161</v>
+        <v>0.07494601430285308</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1023541453428864</v>
+        <v>0.104602510460251</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>48.50746268656716</v>
+        <v>49.25373134328358</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>50.18672403441664</v>
+        <v>49.97840572114123</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>49.011241090922</v>
+        <v>49.47113365664087</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.275870201092049</v>
+        <v>7.274102471405112</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11174.04612474674</v>
+        <v>11165.25271550994</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2552845239414484</v>
+        <v>-0.2391106201459089</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.11481387655449</v>
+        <v>10.11422463332551</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15534.00399898343</v>
+        <v>15524.64712951746</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.03529312963710263</v>
+        <v>0.05797328800476054</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3956,6 +3956,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>14673.95</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.507462686567</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.0749460143029</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -3996,7 +4029,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-07</t>
+          <t>Retrieved 2026-10-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14673.95</v>
+        <v>14867.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>9.56</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5074626865671642</v>
+        <v>0.5149253731343284</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1534.932008368201</v>
+        <v>1535.898760330579</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07494601430285308</v>
+        <v>0.0751858314842373</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.104602510460251</v>
+        <v>0.1033057851239669</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>49.25373134328358</v>
+        <v>48.50746268656716</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>49.97840572114123</v>
+        <v>50.07433259369492</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>49.47113365664087</v>
+        <v>48.97752365870549</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.274102471405112</v>
+        <v>7.274916479437925</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11165.25271550994</v>
+        <v>11173.53520227721</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2391106201459089</v>
+        <v>-0.2484590413803797</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.11422463332551</v>
+        <v>10.11449596933645</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15524.64712951746</v>
+        <v>15534.84182067249</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.05797328800476054</v>
+        <v>0.04488594724550121</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3989,6 +3989,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>14867.5</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.514925373134</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.07518583148419999</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4029,7 +4062,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-08</t>
+          <t>Retrieved 2026-10-09</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14867.5</v>
+        <v>14842.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1535.898760330579</v>
+        <v>1534.932781799379</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0751858314842373</v>
+        <v>0.07425734246595184</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1033057851239669</v>
+        <v>0.1034126163391934</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>50.07433259369492</v>
+        <v>49.70293698638073</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>48.97752365870549</v>
+        <v>48.86610497651123</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.274916479437925</v>
+        <v>7.271764922427288</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11173.53520227721</v>
+        <v>11161.67036097246</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2484590413803797</v>
+        <v>-0.2480077639682227</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.11449596933645</v>
+        <v>10.1134454503329</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15534.84182067249</v>
+        <v>15523.45895865576</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.04488594724550121</v>
+        <v>0.04585785422263733</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4022,6 +4022,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>14842.8</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.514925373134</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.07425734246600001</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4062,7 +4095,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-09</t>
+          <t>Retrieved 2026-10-12</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14842.8</v>
+        <v>14969.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>9.67</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1534.932781799379</v>
+        <v>1535.297435897436</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07425734246595184</v>
+        <v>0.07434693890437027</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1034126163391934</v>
+        <v>0.1025641025641026</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>49.70293698638073</v>
+        <v>49.73877556174811</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>48.86610497651123</v>
+        <v>48.87685654912144</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.271764922427288</v>
+        <v>7.272069038338262</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11161.67036097246</v>
+        <v>11164.78894822987</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2480077639682227</v>
+        <v>-0.2541467652986398</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.1134454503329</v>
+        <v>10.11354682230323</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15523.45895865576</v>
+        <v>15527.30250411081</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.04585785422263733</v>
+        <v>0.03728685356956207</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3741,7 +3741,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -4055,6 +4055,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>14969.15</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.514925373134</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0.0743469389044</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4095,7 +4128,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-12</t>
+          <t>Retrieved 2026-10-13</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14969.15</v>
+        <v>14975.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1535.297435897436</v>
+        <v>1535.902564102564</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07434693890437027</v>
+        <v>0.07470689841294553</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>49.73877556174811</v>
+        <v>49.88275936517821</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>48.87685654912144</v>
+        <v>48.92005169015047</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.272069038338262</v>
+        <v>7.27329084375594</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11164.78894822987</v>
+        <v>11171.06605638845</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2541467652986398</v>
+        <v>-0.2540214519224677</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.11354682230323</v>
+        <v>10.11395409077579</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15527.30250411081</v>
+        <v>15534.04802123815</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.03728685356956207</v>
+        <v>0.03732862469495246</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4088,6 +4088,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>14975.05</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.514925373134</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.0747068984129</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4128,7 +4161,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-13</t>
+          <t>Retrieved 2026-10-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14975.05</v>
+        <v>14962.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>9.75</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1535.902564102564</v>
+        <v>1537.73381294964</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07470689841294553</v>
+        <v>0.07644467992222626</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1025641025641026</v>
+        <v>0.1027749229188078</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>49.88275936517821</v>
+        <v>50.5778719688905</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>48.92005169015047</v>
+        <v>49.12858547126416</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.27329084375594</v>
+        <v>7.279189370707442</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11171.06605638845</v>
+        <v>11193.45562620045</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2540214519224677</v>
+        <v>-0.2518818735141376</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.11395409077579</v>
+        <v>10.11592026642629</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15534.04802123815</v>
+        <v>15555.59264278624</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.03732862469495246</v>
+        <v>0.03966292563476781</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4121,6 +4121,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>14962.15</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.514925373134</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>0.0764446799222</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4161,7 +4194,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-14</t>
+          <t>Retrieved 2026-10-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14962.15</v>
+        <v>14968.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1537.73381294964</v>
+        <v>1538.381294964029</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07644467992222626</v>
+        <v>0.07623166729558695</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>50.5778719688905</v>
+        <v>50.49266691823478</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>49.12858547126416</v>
+        <v>49.10302395606745</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.279189370707442</v>
+        <v>7.278466344991877</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11193.45562620045</v>
+        <v>11197.0564811607</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2518818735141376</v>
+        <v>-0.2519561824263231</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.11592026642629</v>
+        <v>10.11567925785443</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15555.59264278624</v>
+        <v>15561.77175613887</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.03966292563476781</v>
+        <v>0.03963815599737242</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4154,6 +4154,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>14968.45</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.514925373134</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.07623166729560001</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4194,7 +4227,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-15</t>
+          <t>Retrieved 2026-10-16</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14968.45</v>
+        <v>14924.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>9.73</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1538.381294964029</v>
+        <v>1541.740702479339</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07623166729558695</v>
+        <v>0.07834035406017748</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1027749229188078</v>
+        <v>0.1033057851239669</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>50.49266691823478</v>
+        <v>51.33614162407099</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>49.10302395606745</v>
+        <v>49.35606636781831</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.278466344991877</v>
+        <v>7.285623830352831</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11197.0564811607</v>
+        <v>11232.54280220839</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2519561824263231</v>
+        <v>-0.2473529100875174</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.11567925785443</v>
+        <v>10.11806508630809</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15561.77175613887</v>
+        <v>15599.4327738963</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.03963815599737242</v>
+        <v>0.0452546576764552</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4187,6 +4187,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>14924.05</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.514925373134</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.0783403540602</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4227,7 +4260,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-16</t>
+          <t>Retrieved 2026-10-19</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14924.05</v>
+        <v>14772.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>9.68</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1541.740702479339</v>
+        <v>1541.988517745303</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07834035406017748</v>
+        <v>0.08643862218333687</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1033057851239669</v>
+        <v>0.104384133611691</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>51.33614162407099</v>
+        <v>54.57544887333474</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>49.35606636781831</v>
+        <v>50.32785854259743</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.285623830352831</v>
+        <v>7.317482221538302</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11232.54280220839</v>
+        <v>11283.47356441745</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2473529100875174</v>
+        <v>-0.2361709580857723</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.11806508630809</v>
+        <v>10.14168309472515</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15599.4327738963</v>
+        <v>15638.35888267784</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.0452546576764552</v>
+        <v>0.0586308032072187</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4220,6 +4220,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>14772.25</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.514925373134</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.08643862218330001</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4260,7 +4293,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-19</t>
+          <t>Retrieved 2026-10-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14772.25</v>
+        <v>14711.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>9.58</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5149253731343284</v>
+        <v>0.5</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1541.988517745303</v>
+        <v>1542.06498951782</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08643862218333687</v>
+        <v>0.08649250188880364</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.104384133611691</v>
+        <v>0.1048218029350105</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>48.50746268656716</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>54.57544887333474</v>
+        <v>54.59700075552146</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>50.32785854259743</v>
+        <v>51.37910022665643</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.317482221538302</v>
+        <v>7.317726065691042</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11283.47356441745</v>
+        <v>11284.40916878413</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2361709580857723</v>
+        <v>-0.2329427604097439</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.14168309472515</v>
+        <v>10.14186597783971</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15638.35888267784</v>
+        <v>15639.41645280853</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.0586308032072187</v>
+        <v>0.06308867692240172</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4253,6 +4253,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>14711.3</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.08649250188880001</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4293,7 +4326,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-21</t>
+          <t>Retrieved 2026-10-22</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14711.3</v>
+        <v>14451.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>9.539999999999999</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1542.06498951782</v>
+        <v>1542.283884738527</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08649250188880364</v>
+        <v>0.08630740151279825</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1048218029350105</v>
+        <v>0.1067235859124867</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>54.59700075552146</v>
+        <v>54.5229606051193</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>51.37910022665643</v>
+        <v>51.35688818153579</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.317726065691042</v>
+        <v>7.316888354275065</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11284.40916878413</v>
+        <v>11284.71899522944</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2329427604097439</v>
+        <v>-0.2191154371104519</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.14186597783971</v>
+        <v>10.14123769427773</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15639.41645280853</v>
+        <v>15640.66746718744</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.06308867692240172</v>
+        <v>0.08230925232419706</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4286,6 +4286,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>14451.2</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.0863074015128</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4326,7 +4359,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-22</t>
+          <t>Retrieved 2026-10-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14451.2</v>
+        <v>14590.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>9.369999999999999</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1542.283884738527</v>
+        <v>1540.755015839493</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08630740151279825</v>
+        <v>0.08447534721293559</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1067235859124867</v>
+        <v>0.1055966209081309</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>54.5229606051193</v>
+        <v>53.79013888517424</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>51.35688818153579</v>
+        <v>51.13704166555227</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.316888354275065</v>
+        <v>7.308596999957971</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11284.71899522944</v>
+        <v>11260.75748643472</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2191154371104519</v>
+        <v>-0.2282368532251351</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.14123769427773</v>
+        <v>10.13501917853991</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15640.66746718744</v>
+        <v>15615.58163496482</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.08230925232419706</v>
+        <v>0.07022377809291513</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4319,6 +4319,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>14590.95</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.0844753472129</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4359,7 +4392,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-23</t>
+          <t>Retrieved 2026-10-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14590.95</v>
+        <v>14615.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>9.470000000000001</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1540.755015839493</v>
+        <v>1541.698312236287</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08447534721293559</v>
+        <v>0.08501665756117016</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1055966209081309</v>
+        <v>0.1054852320675105</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>53.79013888517424</v>
+        <v>54.00666302446806</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>51.13704166555227</v>
+        <v>51.20199890734042</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.308596999957971</v>
+        <v>7.311046815933981</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11260.75748643472</v>
+        <v>11271.4285368059</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2282368532251351</v>
+        <v>-0.22879252996477</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.13501917853991</v>
+        <v>10.13685654052192</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15615.58163496482</v>
+        <v>15627.974619904</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.07022377809291513</v>
+        <v>0.06928866461201633</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4352,6 +4352,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>14615.3</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>0.0850166575612</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4392,7 +4425,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-26</t>
+          <t>Retrieved 2026-10-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14615.3</v>
+        <v>14595.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1541.698312236287</v>
+        <v>1539.636075949367</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08501665756117016</v>
+        <v>0.06086445314773004</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>54.00666302446806</v>
+        <v>44.34578125909201</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>51.20199890734042</v>
+        <v>48.30373437772761</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.311046815933981</v>
+        <v>7.2</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11271.4285368059</v>
+        <v>11085.37974683544</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.22879252996477</v>
+        <v>-0.2405063291139241</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.13685654052192</v>
+        <v>10.05829235270429</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15627.974619904</v>
+        <v>15486.10976866916</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.06928866461201633</v>
+        <v>0.06100130302787843</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4385,6 +4385,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>14595.75</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0.0608644531477</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4425,7 +4458,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-27</t>
+          <t>Retrieved 2026-10-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14595.75</v>
+        <v>14772.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>9.48</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5</v>
+        <v>0.5149253731343284</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1539.636075949367</v>
+        <v>1538.755208333333</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.06086445314773004</v>
+        <v>0.06056552409971694</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1054852320675105</v>
+        <v>0.1041666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>50</v>
+        <v>48.50746268656716</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>44.34578125909201</v>
+        <v>44.22620963988678</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>48.30373437772761</v>
+        <v>47.22308677256304</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>7.2</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11085.37974683544</v>
+        <v>11079.0375</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2405063291139241</v>
+        <v>-0.2499999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.05829235270429</v>
+        <v>10.05795413583854</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15486.10976866916</v>
+        <v>15476.72931169934</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.06100130302787843</v>
+        <v>0.0477035558165142</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4418,6 +4418,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>14772.05</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.514925373134</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>0.0605655240997</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4458,7 +4491,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-28</t>
+          <t>Retrieved 2026-10-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty500-value-50.xlsx
+++ b/docs/downloads/indices/nifty500-value-50.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14772.05</v>
+        <v>14651.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>9.6</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5149253731343284</v>
+        <v>0.5</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1538.755208333333</v>
+        <v>1563.649946638207</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.06056552409971694</v>
+        <v>0.07797099154238141</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1041666666666667</v>
+        <v>0.1067235859124867</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>48.50746268656716</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>44.22620963988678</v>
+        <v>51.18839661695256</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>47.22308677256304</v>
+        <v>50.35651898508577</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.2</v>
+        <v>7.284370108435283</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11079.0375</v>
+        <v>11390.20493134778</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2499999999999999</v>
+        <v>-0.2225859009140572</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.05795413583854</v>
+        <v>10.11764717900224</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15476.72931169934</v>
+        <v>15820.45847155106</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.0477035558165142</v>
+        <v>0.07979158794047359</v>
       </c>
     </row>
     <row r="16">
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4451,6 +4451,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>14651.4</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>0.0779709915424</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4491,7 +4524,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-29</t>
+          <t>Retrieved 2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
